--- a/output/roomself_excel/2026.xlsx
+++ b/output/roomself_excel/2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>223795</v>
+        <v>104781</v>
       </c>
       <c r="D2" t="n">
-        <v>4444</v>
+        <v>2608</v>
       </c>
       <c r="E2" t="n">
-        <v>545</v>
+        <v>330</v>
       </c>
       <c r="F2" t="n">
-        <v>515</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>567060</v>
+        <v>304109</v>
       </c>
       <c r="D3" t="n">
-        <v>7524</v>
+        <v>4516</v>
       </c>
       <c r="E3" t="n">
-        <v>827</v>
+        <v>1320</v>
       </c>
       <c r="F3" t="n">
-        <v>735</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39468</v>
+        <v>81928</v>
       </c>
       <c r="D4" t="n">
-        <v>1676</v>
+        <v>2536</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="F4" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>530098</v>
+        <v>92769</v>
       </c>
       <c r="D5" t="n">
-        <v>9164</v>
+        <v>2440</v>
       </c>
       <c r="E5" t="n">
-        <v>995</v>
+        <v>346</v>
       </c>
       <c r="F5" t="n">
-        <v>828</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92769</v>
+        <v>128894</v>
       </c>
       <c r="D6" t="n">
-        <v>2440</v>
+        <v>2940</v>
       </c>
       <c r="E6" t="n">
-        <v>346</v>
+        <v>470</v>
       </c>
       <c r="F6" t="n">
         <v>313</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32370</v>
+        <v>75183</v>
       </c>
       <c r="D7" t="n">
-        <v>1444</v>
+        <v>2316</v>
       </c>
       <c r="E7" t="n">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>128894</v>
+        <v>39468</v>
       </c>
       <c r="D8" t="n">
-        <v>2940</v>
+        <v>1676</v>
       </c>
       <c r="E8" t="n">
-        <v>470</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
-        <v>313</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>168153</v>
+        <v>32370</v>
       </c>
       <c r="D9" t="n">
-        <v>3464</v>
+        <v>1444</v>
       </c>
       <c r="E9" t="n">
-        <v>545</v>
+        <v>166</v>
       </c>
       <c r="F9" t="n">
-        <v>312</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75183</v>
+        <v>12524</v>
       </c>
       <c r="D10" t="n">
-        <v>2316</v>
+        <v>900</v>
       </c>
       <c r="E10" t="n">
-        <v>202</v>
+        <v>124</v>
       </c>
       <c r="F10" t="n">
-        <v>137</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10605</v>
+        <v>39280</v>
       </c>
       <c r="D11" t="n">
-        <v>824</v>
+        <v>1616</v>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,86 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12524</v>
+        <v>10605</v>
       </c>
       <c r="D12" t="n">
-        <v>900</v>
+        <v>824</v>
       </c>
       <c r="E12" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>567060</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7524</v>
+      </c>
+      <c r="E13" t="n">
+        <v>827</v>
+      </c>
+      <c r="F13" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>168153</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3464</v>
+      </c>
+      <c r="E14" t="n">
+        <v>545</v>
+      </c>
+      <c r="F14" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>223795</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4444</v>
+      </c>
+      <c r="E15" t="n">
+        <v>545</v>
+      </c>
+      <c r="F15" t="n">
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2026.xlsx
+++ b/output/roomself_excel/2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2608</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>330</v>
       </c>
-      <c r="F2" t="n">
-        <v>24</v>
-      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>4516</v>
       </c>
-      <c r="E3" t="n">
-        <v>1320</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>358</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2536</v>
       </c>
-      <c r="E4" t="n">
-        <v>470</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>212</v>
+        <v>446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>188</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>2440</v>
       </c>
-      <c r="E5" t="n">
-        <v>346</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>313</v>
+        <v>289</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>321</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +631,27 @@
       <c r="D6" t="n">
         <v>2940</v>
       </c>
-      <c r="E6" t="n">
-        <v>470</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>313</v>
+        <v>446</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>289</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>2316</v>
       </c>
-      <c r="E7" t="n">
-        <v>202</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>137</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>1676</v>
       </c>
-      <c r="E8" t="n">
-        <v>300</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>168</v>
+        <v>276</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>143</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>1444</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>166</v>
       </c>
-      <c r="F9" t="n">
-        <v>24</v>
-      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +767,20 @@
       <c r="D10" t="n">
         <v>900</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>124</v>
       </c>
-      <c r="F10" t="n">
-        <v>24</v>
-      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +797,12 @@
       <c r="D11" t="n">
         <v>1616</v>
       </c>
-      <c r="E11" t="n">
-        <v>167</v>
-      </c>
-      <c r="F11" t="n">
-        <v>127</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>824</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>105</v>
       </c>
-      <c r="F12" t="n">
-        <v>24</v>
-      </c>
+      <c r="G12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +849,27 @@
       <c r="D13" t="n">
         <v>7524</v>
       </c>
-      <c r="E13" t="n">
-        <v>827</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>735</v>
+        <v>1470</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>764</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -739,11 +887,27 @@
       <c r="D14" t="n">
         <v>3464</v>
       </c>
-      <c r="E14" t="n">
-        <v>545</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>312</v>
+        <v>276</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>521</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -761,11 +925,27 @@
       <c r="D15" t="n">
         <v>4444</v>
       </c>
-      <c r="E15" t="n">
-        <v>545</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>515</v>
+        <v>521</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>491</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
